--- a/artfynd/A 8023-2025 artfynd.xlsx
+++ b/artfynd/A 8023-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96484507</v>
+        <v>96484180</v>
       </c>
       <c r="B2" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530747.1877585032</v>
+        <v>530774</v>
       </c>
       <c r="R2" t="n">
-        <v>6501793.994321412</v>
+        <v>6501770</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,28 +744,17 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96559381</v>
+        <v>96484342</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +784,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530747.1877585032</v>
+        <v>530749</v>
       </c>
       <c r="R3" t="n">
-        <v>6501793.994321412</v>
+        <v>6501773</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,28 +843,17 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,15 +872,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96483700</v>
+        <v>96484507</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,36 +883,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530700.1367146746</v>
+        <v>530747</v>
       </c>
       <c r="R4" t="n">
-        <v>6501943.473606438</v>
+        <v>6501793</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,27 +944,18 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,6 +971,806 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96484351</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>530760</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6501798</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96484848</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>530728</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6501870</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96559381</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>530747</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6501793</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96484225</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>530767</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6501776</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96483756</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>530725</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6501916</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97459772</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>530724</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6501917</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>E-Fin-0244</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96483700</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>530700</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6501943</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96484235</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>530767</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6501776</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8023-2025 artfynd.xlsx
+++ b/artfynd/A 8023-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484180</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484342</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484507</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484351</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484848</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96559381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484225</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96483756</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97459772</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96483700</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,8 +1826,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>